--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Mistral-Small-3.2-24B-Instruct-2506/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Mistral-Small-3.2-24B-Instruct-2506/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="D2">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D3">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E3">
         <v>4</v>
       </c>
       <c r="G3">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H3">
         <v>426</v>
